--- a/measurements/29/Filled_2D_sections/sagittal/week29_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/sagittal/week29_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +591,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.444378346222487</v>
+        <v>2837.641723356009</v>
       </c>
       <c r="D2" t="n">
-        <v>13.75500987797249</v>
+        <v>268.5501928556533</v>
       </c>
       <c r="E2" t="n">
-        <v>12.28364645271767</v>
+        <v>239.8235736006782</v>
       </c>
       <c r="F2" t="n">
         <v>1.11978230006199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4944432905364532</v>
+        <v>0.4944432905364533</v>
       </c>
       <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.69828869047619</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.36235119047619</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.876860119047619</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.8892911585365854</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8892911585365854</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8892911585365854</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>17.36235119047619</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.172991071428571</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.273809523809524</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.69828869047619</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.50581499107674</v>
+      <c r="AF2" s="2" t="n">
+        <v>2861.060090702947</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +662,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.52468768590125</v>
+        <v>2868.253968253968</v>
       </c>
       <c r="D3" t="n">
-        <v>13.72643494896773</v>
+        <v>267.9923013846079</v>
       </c>
       <c r="E3" t="n">
-        <v>12.3181394483985</v>
+        <v>240.4970082782563</v>
       </c>
       <c r="F3" t="n">
         <v>1.114326965242492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5018602870455879</v>
+        <v>0.501860287045588</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.702008928571428</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.94196428571428</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.789434523809523</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.8677591463414634</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8677591463414634</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8677591463414634</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>16.94196428571428</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.591517857142857</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.922247023809524</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.702008928571428</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.94053017700591</v>
+      <c r="AF3" s="2" t="n">
+        <v>252.6484463129725</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +733,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.643367043426532</v>
+        <v>2913.492063492063</v>
       </c>
       <c r="D4" t="n">
-        <v>14.35812991421397</v>
+        <v>280.3253935632251</v>
       </c>
       <c r="E4" t="n">
-        <v>12.68572650886163</v>
+        <v>247.6737080301557</v>
       </c>
       <c r="F4" t="n">
         <v>1.131833474746919</v>
@@ -619,24 +752,48 @@
         <v>0.4659065566864163</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.652529761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.13430059523809</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.122953869047619</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.9288300304878049</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9288300304878049</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9288300304878049</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>18.13430059523809</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.678199404761905</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.026785714285714</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.652529761904762</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.01622767986321</v>
+      <c r="AF4" s="2" t="n">
+        <v>234.6025404163769</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +804,72 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.692742415229031</v>
+        <v>2932.312925170068</v>
       </c>
       <c r="D5" t="n">
-        <v>14.32608826858241</v>
+        <v>279.6998185770852</v>
       </c>
       <c r="E5" t="n">
-        <v>12.62510988479707</v>
+        <v>246.4902406079428</v>
       </c>
       <c r="F5" t="n">
         <v>1.13472978843801</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4710161620049441</v>
+        <v>0.4710161620049442</v>
       </c>
       <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.94940476190476</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.457093253968252</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16.94940476190476</v>
+      </c>
+      <c r="N5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5221989329268293</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.868140243902439</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6951695884146342</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>10.1953125</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.207217261904762</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.544642857142857</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.075857820343867</v>
       </c>
     </row>
@@ -694,42 +881,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.772754312908983</v>
+        <v>2962.81179138322</v>
       </c>
       <c r="D6" t="n">
-        <v>15.25393288019227</v>
+        <v>297.8148800418491</v>
       </c>
       <c r="E6" t="n">
-        <v>12.48713783810778</v>
+        <v>243.796500648771</v>
       </c>
       <c r="F6" t="n">
-        <v>1.221571594544338</v>
+        <v>1.221571594544339</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4197794191301494</v>
+        <v>0.4197794191301493</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.389508928571429</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.20721726190476</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.468253968253968</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16.20721726190476</v>
+      </c>
+      <c r="N6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5181974085365854</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.830125762195122</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.6741615853658537</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>10.1171875</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.681547619047619</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.96875</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.4453125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.389508928571429</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.5694815708281686</v>
       </c>
     </row>
@@ -741,43 +958,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.911659726353362</v>
+        <v>3015.759637188208</v>
       </c>
       <c r="D7" t="n">
-        <v>13.34007836551201</v>
+        <v>260.4491490409488</v>
       </c>
       <c r="E7" t="n">
-        <v>12.41815180022542</v>
+        <v>242.4496303853534</v>
       </c>
       <c r="F7" t="n">
         <v>1.074240239620026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.558676884658543</v>
+        <v>0.5586768846585429</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5268673780487805</v>
+        <v>1.294642857142857</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5268673780487805</v>
+        <v>10.28645833333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5268673780487805</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>5.105716765873016</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10.28645833333333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.477678571428571</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6.625744047619047</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.523065476190476</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.294642857142857</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.5</v>
+      <c r="AF7" s="2" t="n">
+        <v>5.85</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1035,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.904223676383106</v>
+        <v>3012.925170068027</v>
       </c>
       <c r="D8" t="n">
-        <v>13.13903834180134</v>
+        <v>256.5240819113595</v>
       </c>
       <c r="E8" t="n">
-        <v>12.30875470580124</v>
+        <v>240.3137823513576</v>
       </c>
       <c r="F8" t="n">
         <v>1.067454722743705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5753629939771404</v>
+        <v>0.5753629939771406</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5315358231707318</v>
+        <v>1.333705357142857</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5315358231707318</v>
+        <v>10.37760416666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5315358231707318</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>5.485119047619047</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10.37760416666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.475818452380952</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.164806547619047</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.073660714285714</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.333705357142857</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6626333841463414</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.574776785714286</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1109,70 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.799226650803094</v>
+        <v>2972.902494331066</v>
       </c>
       <c r="D9" t="n">
-        <v>13.05229813878129</v>
+        <v>254.8305827095395</v>
       </c>
       <c r="E9" t="n">
-        <v>12.27426168104497</v>
+        <v>239.6403471061161</v>
       </c>
       <c r="F9" t="n">
         <v>1.063387638128803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5752908078283441</v>
+        <v>0.5752908078283442</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5163871951219512</v>
+        <v>1.508556547619047</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5163871951219512</v>
+        <v>10.08184523809524</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5163871951219512</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5.028831845238096</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.242931547619047</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10.08184523809524</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.752232142857143</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.508556547619047</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7448670922256098</v>
+      <c r="AF9" s="2" t="n">
+        <v>11.23018973214286</v>
       </c>
     </row>
     <row r="10">
@@ -882,34 +1183,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.719809637120762</v>
+        <v>2942.630385487528</v>
       </c>
       <c r="D10" t="n">
-        <v>13.00596897776534</v>
+        <v>253.9260609944661</v>
       </c>
       <c r="E10" t="n">
-        <v>12.24813805847633</v>
+        <v>239.1303144750141</v>
       </c>
       <c r="F10" t="n">
         <v>1.061873152937278</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5734968378857821</v>
+        <v>0.5734968378857823</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.581473214285714</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.893353174603174</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9.581473214285714</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.544642857142857</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.329241071428571</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.545386904761905</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7037502381859756</v>
+      <c r="AF10" s="2" t="n">
+        <v>4.939837992488662</v>
       </c>
     </row>
     <row r="11">
@@ -920,17 +1260,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.639202855443189</v>
+        <v>2911.904761904761</v>
       </c>
       <c r="D11" t="n">
-        <v>12.93453159855633</v>
+        <v>252.5313312099093</v>
       </c>
       <c r="E11" t="n">
-        <v>12.26834358238592</v>
+        <v>239.5248032751537</v>
       </c>
       <c r="F11" t="n">
         <v>1.054301382390927</v>
@@ -939,7 +1279,54 @@
         <v>0.5737946497768996</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.568080357142857</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.655877976190476</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.866381448412699</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9.655877976190476</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.540922619047619</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.649181547619047</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.080357142857143</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.568080357142857</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -950,26 +1337,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.566329565734682</v>
+        <v>2884.126984126984</v>
       </c>
       <c r="D12" t="n">
-        <v>12.71328603058327</v>
+        <v>248.2117748828161</v>
       </c>
       <c r="E12" t="n">
-        <v>12.08996045298693</v>
+        <v>236.0420850345066</v>
       </c>
       <c r="F12" t="n">
         <v>1.051557288381563</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5882737662693835</v>
+        <v>0.5882737662693837</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.287202380952381</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.025297619047619</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.207323554421769</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9.025297619047619</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.390252976190475</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.647321428571428</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.287202380952381</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.6171875</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>17.11904761904761</v>
       </c>
     </row>
     <row r="13">
@@ -980,26 +1414,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.491374182034503</v>
+        <v>2855.555555555555</v>
       </c>
       <c r="D13" t="n">
-        <v>12.62409448332903</v>
+        <v>246.4704161030905</v>
       </c>
       <c r="E13" t="n">
-        <v>12.00913831082786</v>
+        <v>234.4641289256868</v>
       </c>
       <c r="F13" t="n">
         <v>1.051207351983506</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5907053188301169</v>
+        <v>0.5907053188301171</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.30766369047619</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.720238095238095</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.154708758503402</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8.720238095238095</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.945684523809524</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.535714285714286</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.30766369047619</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.686011904761905</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.970331101190476</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="14">
@@ -1010,26 +1491,70 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.467876264128495</v>
+        <v>2846.598639455782</v>
       </c>
       <c r="D14" t="n">
-        <v>12.30182122602695</v>
+        <v>240.1784144129072</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85096071696863</v>
+        <v>231.3758997122447</v>
       </c>
       <c r="F14" t="n">
         <v>1.038044215977593</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6201091714582357</v>
+        <v>0.6201091714582356</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.428199404761905</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.601456207482994</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8.428199404761905</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.17485119047619</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.321428571428572</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>8.930627349624061</v>
       </c>
     </row>
     <row r="15">
@@ -1040,17 +1565,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.373289708506841</v>
+        <v>2810.544217687075</v>
       </c>
       <c r="D15" t="n">
-        <v>12.12690482488493</v>
+        <v>236.76337991442</v>
       </c>
       <c r="E15" t="n">
-        <v>11.64992072814848</v>
+        <v>227.4508332638513</v>
       </c>
       <c r="F15" t="n">
         <v>1.040943119517024</v>
@@ -1059,7 +1584,48 @@
         <v>0.6300444991505223</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.239583333333333</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.350074404761905</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.789372519841269</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8.350074404761905</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.239583333333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.433779761904762</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.877232142857142</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>6.178170787545787</v>
       </c>
     </row>
     <row r="16">
@@ -1070,26 +1636,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.327781082688876</v>
+        <v>2793.197278911564</v>
       </c>
       <c r="D16" t="n">
-        <v>12.1411923257316</v>
+        <v>237.0423263595218</v>
       </c>
       <c r="E16" t="n">
-        <v>11.61542772083748</v>
+        <v>226.7773983592079</v>
       </c>
       <c r="F16" t="n">
         <v>1.045264334429195</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6246829792763154</v>
+        <v>0.6246829792763156</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.005208333333333</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.693266369047619</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.504464285714285</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.005208333333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.764880952380952</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.731026785714286</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>5.757440476190476</v>
       </c>
     </row>
     <row r="17">
@@ -1100,26 +1707,67 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.284651992861392</v>
+        <v>2776.757369614512</v>
       </c>
       <c r="D17" t="n">
-        <v>12.08996047333973</v>
+        <v>236.042085431871</v>
       </c>
       <c r="E17" t="n">
-        <v>11.56664720977225</v>
+        <v>225.8250169526963</v>
       </c>
       <c r="F17" t="n">
         <v>1.045243297740192</v>
       </c>
       <c r="G17" t="n">
-        <v>0.626280531172498</v>
+        <v>0.6262805311724982</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8.725818452380953</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.658544146825397</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.725818452380953</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.930431547619047</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.645089285714286</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>4.242931547619047</v>
       </c>
     </row>
     <row r="18">
@@ -1130,26 +1778,70 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.240928019036288</v>
+        <v>2760.090702947846</v>
       </c>
       <c r="D18" t="n">
-        <v>12.11608406974048</v>
+        <v>236.5521175520761</v>
       </c>
       <c r="E18" t="n">
-        <v>11.52378478864344</v>
+        <v>224.9881792068481</v>
       </c>
       <c r="F18" t="n">
         <v>1.051397981822842</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6198399129649949</v>
+        <v>0.6198399129649951</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.157738095238095</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.064360119047619</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.203125</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9.064360119047619</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.006696428571428</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.911086309523809</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.875744047619047</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.157738095238095</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>10.08184523809524</v>
       </c>
     </row>
     <row r="19">
@@ -1160,26 +1852,70 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.197204045211184</v>
+        <v>2743.424036281179</v>
       </c>
       <c r="D19" t="n">
-        <v>11.95545515490741</v>
+        <v>233.416029214859</v>
       </c>
       <c r="E19" t="n">
-        <v>11.44642936601871</v>
+        <v>223.4779066698892</v>
       </c>
       <c r="F19" t="n">
         <v>1.044470268641141</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6327635441655265</v>
+        <v>0.6327635441655266</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9.322916666666666</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.618551587301587</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9.322916666666666</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.928571428571428</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.966889880952381</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.114955357142857</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>6.752232142857143</v>
       </c>
     </row>
     <row r="20">
@@ -1190,17 +1926,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.131171921475313</v>
+        <v>2718.253968253968</v>
       </c>
       <c r="D20" t="n">
-        <v>12.02444115499171</v>
+        <v>234.7628987403143</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41785441084606</v>
+        <v>222.9200146879469</v>
       </c>
       <c r="F20" t="n">
         <v>1.053126158586279</v>
@@ -1209,7 +1945,51 @@
         <v>0.6197848669941101</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.183035714285714</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.540550595238095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.461150085034014</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9.540550595238095</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.915550595238095</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.183035714285714</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.227306547619047</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.15438988095238</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="21">
@@ -1220,26 +2000,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.983640690065438</v>
+        <v>2662.018140589569</v>
       </c>
       <c r="D21" t="n">
-        <v>11.82585248423786</v>
+        <v>230.8856913589296</v>
       </c>
       <c r="E21" t="n">
-        <v>11.23701993139779</v>
+        <v>219.3894367558615</v>
       </c>
       <c r="F21" t="n">
         <v>1.052401130943516</v>
       </c>
       <c r="G21" t="n">
-        <v>0.627518936751408</v>
+        <v>0.6275189367514082</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.162574404761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.343377976190476</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.315263605442176</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>9.343377976190476</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.162574404761905</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.195684523809524</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.310577876984127</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>3.022017045454545</v>
       </c>
     </row>
     <row r="22">
@@ -1249,7 +2070,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>1.962797619047619</v>
       </c>
     </row>
     <row r="23">
@@ -1263,6 +2092,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.536458333333333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1272,6 +2109,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1.46432705026455</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.292410714285714</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.330236579585538</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/29/Filled_2D_sections/sagittal/week29_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/sagittal/week29_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2178,4 +2384,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week29_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2861.060090702947</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.10182190451751</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2662.018140589569</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3015.759637188208</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>252.6484463129725</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.51866041997284</v>
+      </c>
+      <c r="E11" t="n">
+        <v>230.8856913589296</v>
+      </c>
+      <c r="F11" t="n">
+        <v>297.8148800418491</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.075857820343867</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04616936224232929</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.038044215977593</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.221571594544339</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5694815708281686</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06448353629544959</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4197794191301493</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6327635441655266</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9880869341680844</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4442616583193193</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8870412083230168</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.316894273021107</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17.11904761904761</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.7038300646578021</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.20721726190476</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18.13430059523809</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>41</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.458396849593496</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.989417431574748</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.915550595238095</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.37760416666667</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>71</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.322031145204561</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7854716315890015</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.162574404761905</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.164806547619047</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>